--- a/testdata/realdata/sdh_timeslots.xlsx
+++ b/testdata/realdata/sdh_timeslots.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>容量</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,6 +464,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +491,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +518,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -523,6 +543,11 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>155</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>
